--- a/output/nowcast_output.xlsx
+++ b/output/nowcast_output.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Seats" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flips" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Popular Vote" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flips" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -824,7 +825,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.7857</v>
+        <v>0.7835</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -832,7 +833,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.2143</v>
+        <v>0.2165</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -847,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7857</v>
+        <v>0.7835</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -889,7 +890,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.3605</v>
+        <v>0.3622</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -897,16 +898,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.3605</v>
+        <v>0.3622</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2897</v>
+        <v>0.2926</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3498</v>
+        <v>0.3452</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1084,7 +1085,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.6028</v>
+        <v>0.6068</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1092,10 +1093,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.6028</v>
+        <v>0.6068</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3972</v>
+        <v>0.3932</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1734,7 +1735,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.9928</v>
+        <v>0.9926</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1745,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9928</v>
+        <v>0.9926</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0072</v>
+        <v>0.0074</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1864,7 +1865,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.9344</v>
+        <v>0.931</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1872,10 +1873,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9344</v>
+        <v>0.931</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2189,7 +2190,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.6408</v>
+        <v>0.642</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2197,16 +2198,16 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.6408</v>
+        <v>0.642</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0021</v>
+        <v>0.0024</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3571</v>
+        <v>0.3556</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2319,7 +2320,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.9979</v>
+        <v>0.9973</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2327,10 +2328,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.9979</v>
+        <v>0.9973</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0021</v>
+        <v>0.0027</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2514,7 +2515,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.9901</v>
+        <v>0.9911</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2522,7 +2523,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0089</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -2537,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9901</v>
+        <v>0.9911</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3148,7 +3149,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0.6508</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3159,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6508</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3171,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3492</v>
+        <v>0.3533</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3213,7 +3214,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.9774</v>
+        <v>0.9798</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3221,7 +3222,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.0226</v>
+        <v>0.0202</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3242,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0.9774</v>
+        <v>0.9798</v>
       </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
@@ -3278,7 +3279,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0.6669</v>
+        <v>0.6674</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3289,13 +3290,13 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3331</v>
+        <v>0.3326</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.6669</v>
+        <v>0.6674</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -3538,7 +3539,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.9512</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3546,7 +3547,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.0488</v>
+        <v>0.0489</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -3558,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.9512</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -3863,7 +3864,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.986</v>
+        <v>0.9872</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3871,7 +3872,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.014</v>
+        <v>0.0128</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -3892,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>0.986</v>
+        <v>0.9872</v>
       </c>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
@@ -4058,7 +4059,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.9845</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4066,7 +4067,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.9845</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -4075,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.0155</v>
+        <v>0.0146</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -4318,7 +4319,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.9825</v>
+        <v>0.9848</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4326,7 +4327,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.0175</v>
+        <v>0.0152</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -4335,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0.9825</v>
+        <v>0.9848</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -4708,7 +4709,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4719,13 +4720,13 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -5163,7 +5164,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0.9849</v>
+        <v>0.983</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -5171,10 +5172,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.9849</v>
+        <v>0.983</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0151</v>
+        <v>0.017</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5228,7 +5229,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -5236,16 +5237,16 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -5293,7 +5294,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.8948</v>
+        <v>0.8919</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -5304,13 +5305,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8948</v>
+        <v>0.8919</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.1052</v>
+        <v>0.1081</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -5358,7 +5359,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0.9883</v>
+        <v>0.9888</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -5366,7 +5367,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.0117</v>
+        <v>0.0112</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -5387,7 +5388,7 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>0.9883</v>
+        <v>0.9888</v>
       </c>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
@@ -6203,7 +6204,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0.9981</v>
+        <v>0.9968</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -6211,7 +6212,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.0019</v>
+        <v>0.0032</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -6223,7 +6224,7 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0.9981</v>
+        <v>0.9968</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -6463,7 +6464,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0.763</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -6471,7 +6472,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0.237</v>
+        <v>0.2434</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -6483,7 +6484,7 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0.763</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -6528,7 +6529,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0.9319</v>
+        <v>0.9322</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -6536,7 +6537,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0.9319</v>
+        <v>0.9322</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
@@ -6548,7 +6549,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0678</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -6658,7 +6659,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0.5085</v>
+        <v>0.5132</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -6669,13 +6670,13 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0.5085</v>
+        <v>0.5132</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.4915</v>
+        <v>0.4868</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -6788,7 +6789,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9822</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -6799,13 +6800,13 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0197</v>
+        <v>0.0178</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9822</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -6853,7 +6854,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0.755</v>
+        <v>0.7511</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -6864,13 +6865,13 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0.245</v>
+        <v>0.2489</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0.755</v>
+        <v>0.7511</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -6983,7 +6984,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.965</v>
+        <v>0.9646</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -6991,16 +6992,16 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.0339</v>
+        <v>0.0351</v>
       </c>
       <c r="I101" t="n">
-        <v>0.965</v>
+        <v>0.9646</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>0.0011</v>
+        <v>0.0003</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -7178,7 +7179,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>0.9756</v>
+        <v>0.976</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -7186,7 +7187,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0.9756</v>
+        <v>0.976</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
@@ -7195,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>0.0244</v>
+        <v>0.024</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -7243,7 +7244,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0.8638</v>
+        <v>0.8627</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -7251,7 +7252,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.8638</v>
+        <v>0.8627</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
@@ -7260,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>0.1362</v>
+        <v>0.1373</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -7568,7 +7569,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0.9651</v>
+        <v>0.9648</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -7576,7 +7577,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0.9651</v>
+        <v>0.9648</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
@@ -7585,7 +7586,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>0.0349</v>
+        <v>0.0352</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -7698,7 +7699,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0.8155</v>
+        <v>0.8168</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -7706,7 +7707,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>0.8155</v>
+        <v>0.8168</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -7718,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>0.1845</v>
+        <v>0.1832</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
@@ -8088,7 +8089,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0.9881</v>
+        <v>0.9857</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -8096,7 +8097,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>0.9881</v>
+        <v>0.9857</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -8114,7 +8115,7 @@
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>0.0119</v>
+        <v>0.0143</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -8478,7 +8479,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0.9754</v>
+        <v>0.9771</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -8489,13 +8490,13 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0246</v>
+        <v>0.0229</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>0.9754</v>
+        <v>0.9771</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -8803,7 +8804,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0.9273</v>
+        <v>0.9251</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -8811,10 +8812,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>0.0727</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9273</v>
+        <v>0.9251</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -9388,7 +9389,7 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -9396,10 +9397,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -9583,7 +9584,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -9591,10 +9592,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -9843,7 +9844,7 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0.8747</v>
+        <v>0.8744</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -9851,7 +9852,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>0.1253</v>
+        <v>0.1256</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
@@ -9860,7 +9861,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>0.8747</v>
+        <v>0.8744</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -9908,7 +9909,7 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0.9866</v>
+        <v>0.9897</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -9916,16 +9917,16 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0131</v>
+        <v>0.0101</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>0.9866</v>
+        <v>0.9897</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -9973,7 +9974,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>0.9997</v>
+        <v>0.9999</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -9981,7 +9982,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
@@ -9996,7 +9997,7 @@
         <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>0.9997</v>
+        <v>0.9999</v>
       </c>
       <c r="N147" t="n">
         <v>0</v>
@@ -10038,7 +10039,7 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>0.5366</v>
+        <v>0.5416</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -10046,7 +10047,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>0.5366</v>
+        <v>0.5416</v>
       </c>
       <c r="I148" t="n">
         <v>0</v>
@@ -10055,7 +10056,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>0.4634</v>
+        <v>0.4584</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -10103,7 +10104,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>0.9993</v>
+        <v>0.9997</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -10111,16 +10112,16 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0003</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>0.9993</v>
+        <v>0.9997</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -10168,7 +10169,7 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>0.7722</v>
+        <v>0.7639</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -10179,13 +10180,13 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>0.7722</v>
+        <v>0.7639</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>0.2278</v>
+        <v>0.2361</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -10428,7 +10429,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -10436,7 +10437,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
@@ -10445,7 +10446,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -10493,7 +10494,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>0.5078</v>
+        <v>0.5046</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -10501,7 +10502,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>0.5078</v>
+        <v>0.5046</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
@@ -10516,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>0.4922</v>
+        <v>0.4954</v>
       </c>
       <c r="N155" t="n">
         <v>0</v>
@@ -10623,7 +10624,7 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>0.5844</v>
+        <v>0.5839</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -10631,7 +10632,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>0.4156</v>
+        <v>0.4161</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
@@ -10640,7 +10641,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>0.5844</v>
+        <v>0.5839</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -11078,7 +11079,7 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>0.9889</v>
+        <v>0.991</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -11089,13 +11090,13 @@
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0111</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>0.9889</v>
+        <v>0.991</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -11208,7 +11209,7 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -11219,13 +11220,13 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -11923,7 +11924,7 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>0.9967</v>
+        <v>0.9971</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -11934,13 +11935,13 @@
         <v>0</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9967</v>
+        <v>0.9971</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>0.0033</v>
+        <v>0.0029</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -12183,7 +12184,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>0.9892</v>
+        <v>0.9893</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -12194,7 +12195,7 @@
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>0.0108</v>
+        <v>0.0107</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -12206,7 +12207,7 @@
         <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>0.9892</v>
+        <v>0.9893</v>
       </c>
       <c r="N181" t="n">
         <v>0</v>
@@ -12313,7 +12314,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>0.999</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -12321,7 +12322,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>0.001</v>
+        <v>0.0005</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
@@ -12336,7 +12337,7 @@
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>0.999</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="N183" t="n">
         <v>0</v>
@@ -12378,7 +12379,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -12389,13 +12390,13 @@
         <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0015</v>
+        <v>0.0016</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -12703,7 +12704,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -12711,10 +12712,10 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -13024,7 +13025,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>0.8455</v>
+        <v>0.8472</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -13035,10 +13036,10 @@
         <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>0.1545</v>
+        <v>0.1528</v>
       </c>
       <c r="J194" t="n">
-        <v>0.8455</v>
+        <v>0.8472</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
@@ -13345,7 +13346,7 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>0.9935</v>
+        <v>0.9949</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -13353,7 +13354,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>0.0065</v>
+        <v>0.0051</v>
       </c>
       <c r="I199" t="n">
         <v>0</v>
@@ -13362,7 +13363,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>0.9935</v>
+        <v>0.9949</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -14645,7 +14646,7 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>0.9804</v>
+        <v>0.9776</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -14653,7 +14654,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>0.9804</v>
+        <v>0.9776</v>
       </c>
       <c r="I219" t="n">
         <v>0</v>
@@ -14665,7 +14666,7 @@
         <v>0</v>
       </c>
       <c r="L219" t="n">
-        <v>0.0196</v>
+        <v>0.0224</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
@@ -14710,7 +14711,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>0.6705</v>
+        <v>0.6691</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -14721,13 +14722,13 @@
         <v>0</v>
       </c>
       <c r="I220" t="n">
-        <v>0.3295</v>
+        <v>0.3309</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
       </c>
       <c r="K220" t="n">
-        <v>0.6705</v>
+        <v>0.6691</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -14905,7 +14906,7 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -14916,10 +14917,10 @@
         <v>0</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J223" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -14970,7 +14971,7 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>0.9994</v>
+        <v>0.9996</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -14981,13 +14982,13 @@
         <v>0</v>
       </c>
       <c r="I224" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>0.9994</v>
+        <v>0.9996</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -15226,7 +15227,7 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>0.9971</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -15234,10 +15235,10 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>0.9971</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0029</v>
+        <v>0.0035</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -15356,7 +15357,7 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>0.5316</v>
+        <v>0.5261</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -15367,13 +15368,13 @@
         <v>0</v>
       </c>
       <c r="I230" t="n">
-        <v>0.4684</v>
+        <v>0.4739</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
       </c>
       <c r="K230" t="n">
-        <v>0.5316</v>
+        <v>0.5261</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -15547,7 +15548,7 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -15558,13 +15559,13 @@
         <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
       </c>
       <c r="K233" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -15742,7 +15743,7 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>0.9546</v>
+        <v>0.9528</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -15750,7 +15751,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>0.0454</v>
+        <v>0.0472</v>
       </c>
       <c r="I236" t="n">
         <v>0</v>
@@ -15759,7 +15760,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="n">
-        <v>0.9546</v>
+        <v>0.9528</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -16392,7 +16393,7 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>0.5794</v>
+        <v>0.5744</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -16400,16 +16401,16 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>0.2124</v>
+        <v>0.2133</v>
       </c>
       <c r="I246" t="n">
-        <v>0.2082</v>
+        <v>0.2123</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
       </c>
       <c r="K246" t="n">
-        <v>0.5794</v>
+        <v>0.5744</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -16522,7 +16523,7 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -16533,13 +16534,13 @@
         <v>0</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
       </c>
       <c r="K248" t="n">
-        <v>0.0025</v>
+        <v>0.0015</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -16782,7 +16783,7 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>0.8834</v>
+        <v>0.883</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -16790,7 +16791,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>0.1166</v>
+        <v>0.117</v>
       </c>
       <c r="I252" t="n">
         <v>0</v>
@@ -16799,7 +16800,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="n">
-        <v>0.8834</v>
+        <v>0.883</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -16847,7 +16848,7 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>0.9575</v>
+        <v>0.9611</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -16858,13 +16859,13 @@
         <v>0</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0425</v>
+        <v>0.0389</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
       </c>
       <c r="K253" t="n">
-        <v>0.9575</v>
+        <v>0.9611</v>
       </c>
       <c r="L253" t="n">
         <v>0</v>
@@ -16912,7 +16913,7 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -16923,13 +16924,13 @@
         <v>0</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
       </c>
       <c r="K254" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -17302,7 +17303,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>1</v>
+        <v>0.9992</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -17310,7 +17311,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>1</v>
+        <v>0.9992</v>
       </c>
       <c r="I260" t="n">
         <v>0</v>
@@ -17322,7 +17323,7 @@
         <v>0</v>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="M260" t="n">
         <v>0</v>
@@ -17562,7 +17563,7 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>0.534</v>
+        <v>0.5384</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -17570,7 +17571,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>0.466</v>
+        <v>0.4616</v>
       </c>
       <c r="I264" t="n">
         <v>0</v>
@@ -17585,7 +17586,7 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>0.534</v>
+        <v>0.5384</v>
       </c>
       <c r="N264" t="n">
         <v>0</v>
@@ -18602,7 +18603,7 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>0.7798</v>
+        <v>0.7771</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -18610,10 +18611,10 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>0.7798</v>
+        <v>0.7771</v>
       </c>
       <c r="I280" t="n">
-        <v>0.2202</v>
+        <v>0.2229</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -18732,7 +18733,7 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9813</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
@@ -18743,13 +18744,13 @@
         <v>0</v>
       </c>
       <c r="I282" t="n">
-        <v>0.0207</v>
+        <v>0.0187</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9813</v>
       </c>
       <c r="L282" t="n">
         <v>0</v>
@@ -18797,7 +18798,7 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>0.6782</v>
+        <v>0.6781</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
@@ -18808,13 +18809,13 @@
         <v>0</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3218</v>
+        <v>0.3219</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
       </c>
       <c r="K283" t="n">
-        <v>0.6782</v>
+        <v>0.6781</v>
       </c>
       <c r="L283" t="n">
         <v>0</v>
@@ -18862,7 +18863,7 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>0.9264</v>
+        <v>0.9274</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -18873,13 +18874,13 @@
         <v>0</v>
       </c>
       <c r="I284" t="n">
-        <v>0.0736</v>
+        <v>0.0726</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
       </c>
       <c r="K284" t="n">
-        <v>0.9264</v>
+        <v>0.9274</v>
       </c>
       <c r="L284" t="n">
         <v>0</v>
@@ -19122,7 +19123,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>0.9997</v>
+        <v>0.999</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -19130,16 +19131,16 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>0.9997</v>
+        <v>0.999</v>
       </c>
       <c r="I288" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
       </c>
       <c r="K288" t="n">
-        <v>0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="L288" t="n">
         <v>0</v>
@@ -19252,7 +19253,7 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>0.9428</v>
+        <v>0.9373</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
@@ -19260,10 +19261,10 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>0.9428</v>
+        <v>0.9373</v>
       </c>
       <c r="I290" t="n">
-        <v>0.0572</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -20032,7 +20033,7 @@
         </is>
       </c>
       <c r="F302" t="n">
-        <v>0.9516</v>
+        <v>0.9522</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
@@ -20040,7 +20041,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>0.0484</v>
+        <v>0.0478</v>
       </c>
       <c r="I302" t="n">
         <v>0</v>
@@ -20061,7 +20062,7 @@
         <v>0</v>
       </c>
       <c r="O302" t="n">
-        <v>0.9516</v>
+        <v>0.9522</v>
       </c>
       <c r="P302" t="inlineStr"/>
       <c r="Q302" t="inlineStr"/>
@@ -20227,7 +20228,7 @@
         </is>
       </c>
       <c r="F305" t="n">
-        <v>0.8213</v>
+        <v>0.8173</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
@@ -20235,7 +20236,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>0.1787</v>
+        <v>0.1827</v>
       </c>
       <c r="I305" t="n">
         <v>0</v>
@@ -20244,7 +20245,7 @@
         <v>0</v>
       </c>
       <c r="K305" t="n">
-        <v>0.8213</v>
+        <v>0.8173</v>
       </c>
       <c r="L305" t="n">
         <v>0</v>
@@ -20357,7 +20358,7 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -20365,7 +20366,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>0.0005</v>
+        <v>0.0003</v>
       </c>
       <c r="I307" t="n">
         <v>0</v>
@@ -20374,7 +20375,7 @@
         <v>0</v>
       </c>
       <c r="K307" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="L307" t="n">
         <v>0</v>
@@ -21202,7 +21203,7 @@
         </is>
       </c>
       <c r="F320" t="n">
-        <v>0.5258</v>
+        <v>0.5279</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -21213,13 +21214,13 @@
         <v>0</v>
       </c>
       <c r="I320" t="n">
-        <v>0.5258</v>
+        <v>0.5279</v>
       </c>
       <c r="J320" t="n">
         <v>0</v>
       </c>
       <c r="K320" t="n">
-        <v>0.4742</v>
+        <v>0.4721</v>
       </c>
       <c r="L320" t="n">
         <v>0</v>
@@ -21332,7 +21333,7 @@
         </is>
       </c>
       <c r="F322" t="n">
-        <v>0.9873</v>
+        <v>0.9875</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
@@ -21348,13 +21349,13 @@
       <c r="N322" t="inlineStr"/>
       <c r="O322" t="inlineStr"/>
       <c r="P322" t="n">
-        <v>0.0127</v>
+        <v>0.0125</v>
       </c>
       <c r="Q322" t="n">
         <v>0</v>
       </c>
       <c r="R322" t="n">
-        <v>0.9873</v>
+        <v>0.9875</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -21393,7 +21394,7 @@
         </is>
       </c>
       <c r="F323" t="n">
-        <v>0.995</v>
+        <v>0.9949</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
@@ -21401,7 +21402,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>0.995</v>
+        <v>0.9949</v>
       </c>
       <c r="I323" t="n">
         <v>0</v>
@@ -21410,7 +21411,7 @@
         <v>0</v>
       </c>
       <c r="K323" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="L323" t="n">
         <v>0</v>
@@ -21718,7 +21719,7 @@
         </is>
       </c>
       <c r="F328" t="n">
-        <v>0.8756</v>
+        <v>0.8793</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
@@ -21726,7 +21727,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>0.8756</v>
+        <v>0.8793</v>
       </c>
       <c r="I328" t="n">
         <v>0</v>
@@ -21738,7 +21739,7 @@
         <v>0</v>
       </c>
       <c r="L328" t="n">
-        <v>0.1244</v>
+        <v>0.1207</v>
       </c>
       <c r="M328" t="n">
         <v>0</v>
@@ -21848,7 +21849,7 @@
         </is>
       </c>
       <c r="F330" t="n">
-        <v>0.9169</v>
+        <v>0.9125</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
@@ -21856,7 +21857,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>0.9169</v>
+        <v>0.9125</v>
       </c>
       <c r="I330" t="n">
         <v>0</v>
@@ -21865,7 +21866,7 @@
         <v>0</v>
       </c>
       <c r="K330" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="L330" t="n">
         <v>0</v>
@@ -21913,7 +21914,7 @@
         </is>
       </c>
       <c r="F331" t="n">
-        <v>0.7452</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
@@ -21924,7 +21925,7 @@
         <v>0</v>
       </c>
       <c r="I331" t="n">
-        <v>0.7452</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="J331" t="n">
         <v>0</v>
@@ -21942,7 +21943,7 @@
         <v>0</v>
       </c>
       <c r="O331" t="n">
-        <v>0.2548</v>
+        <v>0.2646</v>
       </c>
       <c r="P331" t="inlineStr"/>
       <c r="Q331" t="inlineStr"/>
@@ -22043,7 +22044,7 @@
         </is>
       </c>
       <c r="F333" t="n">
-        <v>0.9123</v>
+        <v>0.909</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
@@ -22051,7 +22052,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>0.0877</v>
+        <v>0.091</v>
       </c>
       <c r="I333" t="n">
         <v>0</v>
@@ -22060,7 +22061,7 @@
         <v>0</v>
       </c>
       <c r="K333" t="n">
-        <v>0.9123</v>
+        <v>0.909</v>
       </c>
       <c r="L333" t="n">
         <v>0</v>
@@ -23343,7 +23344,7 @@
         </is>
       </c>
       <c r="F353" t="n">
-        <v>0.7643</v>
+        <v>0.7581</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
@@ -23351,7 +23352,7 @@
         </is>
       </c>
       <c r="H353" t="n">
-        <v>0.7643</v>
+        <v>0.7581</v>
       </c>
       <c r="I353" t="n">
         <v>0</v>
@@ -23372,7 +23373,7 @@
         <v>0</v>
       </c>
       <c r="O353" t="n">
-        <v>0.2357</v>
+        <v>0.2419</v>
       </c>
       <c r="P353" t="inlineStr"/>
       <c r="Q353" t="inlineStr"/>
@@ -23473,7 +23474,7 @@
         </is>
       </c>
       <c r="F355" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
@@ -23481,10 +23482,10 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
       <c r="I355" t="n">
-        <v>0.0001</v>
+        <v>0.001</v>
       </c>
       <c r="J355" t="n">
         <v>0</v>
@@ -23603,7 +23604,7 @@
         </is>
       </c>
       <c r="F357" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9987</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
@@ -23614,13 +23615,13 @@
         <v>0</v>
       </c>
       <c r="I357" t="n">
-        <v>0.0015</v>
+        <v>0.0013</v>
       </c>
       <c r="J357" t="n">
         <v>0</v>
       </c>
       <c r="K357" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9987</v>
       </c>
       <c r="L357" t="n">
         <v>0</v>
@@ -23863,7 +23864,7 @@
         </is>
       </c>
       <c r="F361" t="n">
-        <v>0.9929</v>
+        <v>0.994</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
@@ -23871,7 +23872,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>0.0071</v>
+        <v>0.006</v>
       </c>
       <c r="I361" t="n">
         <v>0</v>
@@ -23883,7 +23884,7 @@
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>0.9929</v>
+        <v>0.994</v>
       </c>
       <c r="M361" t="n">
         <v>0</v>
@@ -23928,7 +23929,7 @@
         </is>
       </c>
       <c r="F362" t="n">
-        <v>0.9906</v>
+        <v>0.9889</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
@@ -23936,7 +23937,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>0.9906</v>
+        <v>0.9889</v>
       </c>
       <c r="I362" t="n">
         <v>0</v>
@@ -23948,7 +23949,7 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0.0094</v>
+        <v>0.0111</v>
       </c>
       <c r="M362" t="n">
         <v>0</v>
@@ -24123,7 +24124,7 @@
         </is>
       </c>
       <c r="F365" t="n">
-        <v>0.7708</v>
+        <v>0.7627</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
@@ -24134,13 +24135,13 @@
         <v>0</v>
       </c>
       <c r="I365" t="n">
-        <v>0.7708</v>
+        <v>0.7627</v>
       </c>
       <c r="J365" t="n">
         <v>0</v>
       </c>
       <c r="K365" t="n">
-        <v>0.2292</v>
+        <v>0.2373</v>
       </c>
       <c r="L365" t="n">
         <v>0</v>
@@ -24188,7 +24189,7 @@
         </is>
       </c>
       <c r="F366" t="n">
-        <v>0.6332</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
@@ -24199,13 +24200,13 @@
         <v>0</v>
       </c>
       <c r="I366" t="n">
-        <v>0.3668</v>
+        <v>0.3695</v>
       </c>
       <c r="J366" t="n">
         <v>0</v>
       </c>
       <c r="K366" t="n">
-        <v>0.6332</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="L366" t="n">
         <v>0</v>
@@ -24318,7 +24319,7 @@
         </is>
       </c>
       <c r="F368" t="n">
-        <v>0.6614</v>
+        <v>0.6624</v>
       </c>
       <c r="G368" t="inlineStr">
         <is>
@@ -24326,16 +24327,16 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>0.0075</v>
+        <v>0.0063</v>
       </c>
       <c r="I368" t="n">
-        <v>0.3311</v>
+        <v>0.3313</v>
       </c>
       <c r="J368" t="n">
         <v>0</v>
       </c>
       <c r="K368" t="n">
-        <v>0.6614</v>
+        <v>0.6624</v>
       </c>
       <c r="L368" t="n">
         <v>0</v>
@@ -24383,7 +24384,7 @@
         </is>
       </c>
       <c r="F369" t="n">
-        <v>0.9397</v>
+        <v>0.9393</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
@@ -24394,13 +24395,13 @@
         <v>0</v>
       </c>
       <c r="I369" t="n">
-        <v>0.9397</v>
+        <v>0.9393</v>
       </c>
       <c r="J369" t="n">
         <v>0</v>
       </c>
       <c r="K369" t="n">
-        <v>0.0603</v>
+        <v>0.0607</v>
       </c>
       <c r="L369" t="n">
         <v>0</v>
@@ -24513,7 +24514,7 @@
         </is>
       </c>
       <c r="F371" t="n">
-        <v>0.9949</v>
+        <v>0.9954</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
@@ -24521,7 +24522,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>0.0051</v>
+        <v>0.0046</v>
       </c>
       <c r="I371" t="n">
         <v>0</v>
@@ -24530,7 +24531,7 @@
         <v>0</v>
       </c>
       <c r="K371" t="n">
-        <v>0.9949</v>
+        <v>0.9954</v>
       </c>
       <c r="L371" t="n">
         <v>0</v>
@@ -24578,7 +24579,7 @@
         </is>
       </c>
       <c r="F372" t="n">
-        <v>0.994</v>
+        <v>0.9947</v>
       </c>
       <c r="G372" t="inlineStr">
         <is>
@@ -24589,13 +24590,13 @@
         <v>0</v>
       </c>
       <c r="I372" t="n">
-        <v>0.006</v>
+        <v>0.0053</v>
       </c>
       <c r="J372" t="n">
         <v>0</v>
       </c>
       <c r="K372" t="n">
-        <v>0.994</v>
+        <v>0.9947</v>
       </c>
       <c r="L372" t="n">
         <v>0</v>
@@ -24773,7 +24774,7 @@
         </is>
       </c>
       <c r="F375" t="n">
-        <v>0.9321</v>
+        <v>0.9298</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
@@ -24784,13 +24785,13 @@
         <v>0</v>
       </c>
       <c r="I375" t="n">
-        <v>0.9321</v>
+        <v>0.9298</v>
       </c>
       <c r="J375" t="n">
         <v>0</v>
       </c>
       <c r="K375" t="n">
-        <v>0.0679</v>
+        <v>0.0702</v>
       </c>
       <c r="L375" t="n">
         <v>0</v>
@@ -24838,7 +24839,7 @@
         </is>
       </c>
       <c r="F376" t="n">
-        <v>0.9559</v>
+        <v>0.96</v>
       </c>
       <c r="G376" t="inlineStr">
         <is>
@@ -24849,13 +24850,13 @@
         <v>0</v>
       </c>
       <c r="I376" t="n">
-        <v>0.0441</v>
+        <v>0.04</v>
       </c>
       <c r="J376" t="n">
         <v>0</v>
       </c>
       <c r="K376" t="n">
-        <v>0.9559</v>
+        <v>0.96</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
@@ -25159,7 +25160,7 @@
         </is>
       </c>
       <c r="F381" t="n">
-        <v>0.9644</v>
+        <v>0.963</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -25167,7 +25168,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>0.0356</v>
+        <v>0.037</v>
       </c>
       <c r="I381" t="n">
         <v>0</v>
@@ -25182,7 +25183,7 @@
         <v>0</v>
       </c>
       <c r="M381" t="n">
-        <v>0.9644</v>
+        <v>0.963</v>
       </c>
       <c r="N381" t="n">
         <v>0</v>
@@ -25289,7 +25290,7 @@
         </is>
       </c>
       <c r="F383" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -25297,10 +25298,10 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="I383" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="J383" t="n">
         <v>0</v>
@@ -25419,7 +25420,7 @@
         </is>
       </c>
       <c r="F385" t="n">
-        <v>0.9748</v>
+        <v>0.9731</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
@@ -25427,10 +25428,10 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>0.0252</v>
+        <v>0.0269</v>
       </c>
       <c r="I385" t="n">
-        <v>0.9748</v>
+        <v>0.9731</v>
       </c>
       <c r="J385" t="n">
         <v>0</v>
@@ -25622,10 +25623,10 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>0.0322</v>
+        <v>0.0324</v>
       </c>
       <c r="I388" t="n">
-        <v>0.003</v>
+        <v>0.0028</v>
       </c>
       <c r="J388" t="n">
         <v>0</v>
@@ -25679,7 +25680,7 @@
         </is>
       </c>
       <c r="F389" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
@@ -25687,7 +25688,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="I389" t="n">
         <v>0</v>
@@ -25702,7 +25703,7 @@
         <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="N389" t="n">
         <v>0</v>
@@ -27166,7 +27167,7 @@
         </is>
       </c>
       <c r="F412" t="n">
-        <v>0.8186</v>
+        <v>0.8243</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
@@ -27177,10 +27178,10 @@
         <v>0</v>
       </c>
       <c r="I412" t="n">
-        <v>0.8186</v>
+        <v>0.8243</v>
       </c>
       <c r="J412" t="n">
-        <v>0.1814</v>
+        <v>0.1757</v>
       </c>
       <c r="K412" t="n">
         <v>0</v>
@@ -27357,7 +27358,7 @@
         </is>
       </c>
       <c r="F415" t="n">
-        <v>0.5092</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
@@ -27368,13 +27369,13 @@
         <v>0</v>
       </c>
       <c r="I415" t="n">
-        <v>0.5092</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="J415" t="n">
         <v>0</v>
       </c>
       <c r="K415" t="n">
-        <v>0.4908</v>
+        <v>0.4854</v>
       </c>
       <c r="L415" t="n">
         <v>0</v>
@@ -27422,7 +27423,7 @@
         </is>
       </c>
       <c r="F416" t="n">
-        <v>0.7252</v>
+        <v>0.7208</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
@@ -27433,13 +27434,13 @@
         <v>0</v>
       </c>
       <c r="I416" t="n">
-        <v>0.2748</v>
+        <v>0.2792</v>
       </c>
       <c r="J416" t="n">
         <v>0</v>
       </c>
       <c r="K416" t="n">
-        <v>0.7252</v>
+        <v>0.7208</v>
       </c>
       <c r="L416" t="n">
         <v>0</v>
@@ -27617,7 +27618,7 @@
         </is>
       </c>
       <c r="F419" t="n">
-        <v>0.6248</v>
+        <v>0.6221</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
@@ -27628,13 +27629,13 @@
         <v>0</v>
       </c>
       <c r="I419" t="n">
-        <v>0.3752</v>
+        <v>0.3779</v>
       </c>
       <c r="J419" t="n">
         <v>0</v>
       </c>
       <c r="K419" t="n">
-        <v>0.6248</v>
+        <v>0.6221</v>
       </c>
       <c r="L419" t="n">
         <v>0</v>
@@ -27682,7 +27683,7 @@
         </is>
       </c>
       <c r="F420" t="n">
-        <v>0.7923</v>
+        <v>0.7881</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
@@ -27690,16 +27691,16 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>0.2075</v>
+        <v>0.2119</v>
       </c>
       <c r="I420" t="n">
-        <v>0.7923</v>
+        <v>0.7881</v>
       </c>
       <c r="J420" t="n">
         <v>0</v>
       </c>
       <c r="K420" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="L420" t="n">
         <v>0</v>
@@ -28397,7 +28398,7 @@
         </is>
       </c>
       <c r="F431" t="n">
-        <v>0.8303</v>
+        <v>0.8265</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
@@ -28408,13 +28409,13 @@
         <v>0</v>
       </c>
       <c r="I431" t="n">
-        <v>0.8303</v>
+        <v>0.8265</v>
       </c>
       <c r="J431" t="n">
         <v>0</v>
       </c>
       <c r="K431" t="n">
-        <v>0.1697</v>
+        <v>0.1735</v>
       </c>
       <c r="L431" t="n">
         <v>0</v>
@@ -28462,7 +28463,7 @@
         </is>
       </c>
       <c r="F432" t="n">
-        <v>0.9292</v>
+        <v>0.9242</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
@@ -28470,7 +28471,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>0.0708</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="I432" t="n">
         <v>0</v>
@@ -28479,7 +28480,7 @@
         <v>0</v>
       </c>
       <c r="K432" t="n">
-        <v>0.9292</v>
+        <v>0.9242</v>
       </c>
       <c r="L432" t="n">
         <v>0</v>
@@ -28592,7 +28593,7 @@
         </is>
       </c>
       <c r="F434" t="n">
-        <v>0.9972</v>
+        <v>0.9976</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
@@ -28600,7 +28601,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>0.0028</v>
+        <v>0.0024</v>
       </c>
       <c r="I434" t="n">
         <v>0</v>
@@ -28609,7 +28610,7 @@
         <v>0</v>
       </c>
       <c r="K434" t="n">
-        <v>0.9972</v>
+        <v>0.9976</v>
       </c>
       <c r="L434" t="n">
         <v>0</v>
@@ -28657,7 +28658,7 @@
         </is>
       </c>
       <c r="F435" t="n">
-        <v>0.9425</v>
+        <v>0.9404</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
@@ -28665,7 +28666,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>0.0575</v>
+        <v>0.0596</v>
       </c>
       <c r="I435" t="n">
         <v>0</v>
@@ -28677,7 +28678,7 @@
         <v>0</v>
       </c>
       <c r="L435" t="n">
-        <v>0.9425</v>
+        <v>0.9404</v>
       </c>
       <c r="M435" t="n">
         <v>0</v>
@@ -28852,7 +28853,7 @@
         </is>
       </c>
       <c r="F438" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9893</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
@@ -28860,7 +28861,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9893</v>
       </c>
       <c r="I438" t="n">
         <v>0</v>
@@ -28869,7 +28870,7 @@
         <v>0</v>
       </c>
       <c r="K438" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0107</v>
       </c>
       <c r="L438" t="n">
         <v>0</v>
@@ -29112,7 +29113,7 @@
         </is>
       </c>
       <c r="F442" t="n">
-        <v>0.9986</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
@@ -29129,7 +29130,7 @@
         <v>0</v>
       </c>
       <c r="K442" t="n">
-        <v>0.0014</v>
+        <v>0.0005</v>
       </c>
       <c r="L442" t="n">
         <v>0</v>
@@ -29141,7 +29142,7 @@
         <v>0</v>
       </c>
       <c r="O442" t="n">
-        <v>0.9986</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="P442" t="inlineStr"/>
       <c r="Q442" t="inlineStr"/>
@@ -29697,7 +29698,7 @@
         </is>
       </c>
       <c r="F451" t="n">
-        <v>0.6115</v>
+        <v>0.6102</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
@@ -29708,13 +29709,13 @@
         <v>0</v>
       </c>
       <c r="I451" t="n">
-        <v>0.3885</v>
+        <v>0.3898</v>
       </c>
       <c r="J451" t="n">
         <v>0</v>
       </c>
       <c r="K451" t="n">
-        <v>0.6115</v>
+        <v>0.6102</v>
       </c>
       <c r="L451" t="n">
         <v>0</v>
@@ -29827,7 +29828,7 @@
         </is>
       </c>
       <c r="F453" t="n">
-        <v>0.7121</v>
+        <v>0.7094</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
@@ -29835,16 +29836,16 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>0.1508</v>
+        <v>0.1529</v>
       </c>
       <c r="I453" t="n">
-        <v>0.1371</v>
+        <v>0.1377</v>
       </c>
       <c r="J453" t="n">
         <v>0</v>
       </c>
       <c r="K453" t="n">
-        <v>0.7121</v>
+        <v>0.7094</v>
       </c>
       <c r="L453" t="n">
         <v>0</v>
@@ -29957,7 +29958,7 @@
         </is>
       </c>
       <c r="F455" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
@@ -29965,10 +29966,10 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="I455" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="J455" t="n">
         <v>0</v>
@@ -30087,7 +30088,7 @@
         </is>
       </c>
       <c r="F457" t="n">
-        <v>0.9629</v>
+        <v>0.9618</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
@@ -30095,7 +30096,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>0.9629</v>
+        <v>0.9618</v>
       </c>
       <c r="I457" t="n">
         <v>0</v>
@@ -30104,7 +30105,7 @@
         <v>0</v>
       </c>
       <c r="K457" t="n">
-        <v>0.0371</v>
+        <v>0.0382</v>
       </c>
       <c r="L457" t="n">
         <v>0</v>
@@ -30282,7 +30283,7 @@
         </is>
       </c>
       <c r="F460" t="n">
-        <v>0.6797</v>
+        <v>0.6726</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
@@ -30293,13 +30294,13 @@
         <v>0</v>
       </c>
       <c r="I460" t="n">
-        <v>0.6797</v>
+        <v>0.6726</v>
       </c>
       <c r="J460" t="n">
         <v>0</v>
       </c>
       <c r="K460" t="n">
-        <v>0.3203</v>
+        <v>0.3274</v>
       </c>
       <c r="L460" t="n">
         <v>0</v>
@@ -30412,7 +30413,7 @@
         </is>
       </c>
       <c r="F462" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
@@ -30423,13 +30424,13 @@
         <v>0</v>
       </c>
       <c r="I462" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="J462" t="n">
         <v>0</v>
       </c>
       <c r="K462" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="L462" t="n">
         <v>0</v>
@@ -30542,7 +30543,7 @@
         </is>
       </c>
       <c r="F464" t="n">
-        <v>0.6082</v>
+        <v>0.6038</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
@@ -30550,7 +30551,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>0.6082</v>
+        <v>0.6038</v>
       </c>
       <c r="I464" t="n">
         <v>0</v>
@@ -30571,7 +30572,7 @@
         <v>0</v>
       </c>
       <c r="O464" t="n">
-        <v>0.3918</v>
+        <v>0.3962</v>
       </c>
       <c r="P464" t="inlineStr"/>
       <c r="Q464" t="inlineStr"/>
@@ -31257,7 +31258,7 @@
         </is>
       </c>
       <c r="F475" t="n">
-        <v>0.9885</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
@@ -31268,13 +31269,13 @@
         <v>0</v>
       </c>
       <c r="I475" t="n">
-        <v>0.9885</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="J475" t="n">
         <v>0</v>
       </c>
       <c r="K475" t="n">
-        <v>0.0115</v>
+        <v>0.0116</v>
       </c>
       <c r="L475" t="n">
         <v>0</v>
@@ -31452,7 +31453,7 @@
         </is>
       </c>
       <c r="F478" t="n">
-        <v>0.9986</v>
+        <v>0.9996</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
@@ -31469,7 +31470,7 @@
         <v>0</v>
       </c>
       <c r="K478" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="L478" t="n">
         <v>0</v>
@@ -31481,7 +31482,7 @@
         <v>0</v>
       </c>
       <c r="O478" t="n">
-        <v>0.9986</v>
+        <v>0.9996</v>
       </c>
       <c r="P478" t="inlineStr"/>
       <c r="Q478" t="inlineStr"/>
@@ -31582,7 +31583,7 @@
         </is>
       </c>
       <c r="F480" t="n">
-        <v>0.9984</v>
+        <v>0.9997</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
@@ -31593,13 +31594,13 @@
         <v>0</v>
       </c>
       <c r="I480" t="n">
-        <v>0.9984</v>
+        <v>0.9997</v>
       </c>
       <c r="J480" t="n">
         <v>0</v>
       </c>
       <c r="K480" t="n">
-        <v>0.0016</v>
+        <v>0.0003</v>
       </c>
       <c r="L480" t="n">
         <v>0</v>
@@ -31647,7 +31648,7 @@
         </is>
       </c>
       <c r="F481" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9769</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
@@ -31658,10 +31659,10 @@
         <v>0</v>
       </c>
       <c r="I481" t="n">
-        <v>0.0227</v>
+        <v>0.0231</v>
       </c>
       <c r="J481" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9769</v>
       </c>
       <c r="K481" t="n">
         <v>0</v>
@@ -31907,7 +31908,7 @@
         </is>
       </c>
       <c r="F485" t="n">
-        <v>0.9986</v>
+        <v>0.9988</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
@@ -31918,13 +31919,13 @@
         <v>0</v>
       </c>
       <c r="I485" t="n">
-        <v>0.0014</v>
+        <v>0.0012</v>
       </c>
       <c r="J485" t="n">
         <v>0</v>
       </c>
       <c r="K485" t="n">
-        <v>0.9986</v>
+        <v>0.9988</v>
       </c>
       <c r="L485" t="n">
         <v>0</v>
@@ -32037,7 +32038,7 @@
         </is>
       </c>
       <c r="F487" t="n">
-        <v>0.9812</v>
+        <v>0.9807</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
@@ -32045,7 +32046,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>0.9812</v>
+        <v>0.9807</v>
       </c>
       <c r="I487" t="n">
         <v>0</v>
@@ -32054,7 +32055,7 @@
         <v>0</v>
       </c>
       <c r="K487" t="n">
-        <v>0.0188</v>
+        <v>0.0193</v>
       </c>
       <c r="L487" t="n">
         <v>0</v>
@@ -32167,7 +32168,7 @@
         </is>
       </c>
       <c r="F489" t="n">
-        <v>0.7282</v>
+        <v>0.7306</v>
       </c>
       <c r="G489" t="inlineStr">
         <is>
@@ -32175,10 +32176,10 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>0.7282</v>
+        <v>0.7306</v>
       </c>
       <c r="I489" t="n">
-        <v>0.2718</v>
+        <v>0.2694</v>
       </c>
       <c r="J489" t="n">
         <v>0</v>
@@ -32232,7 +32233,7 @@
         </is>
       </c>
       <c r="F490" t="n">
-        <v>0.6609</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
@@ -32240,7 +32241,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>0.3391</v>
+        <v>0.3402</v>
       </c>
       <c r="I490" t="n">
         <v>0</v>
@@ -32255,7 +32256,7 @@
         <v>0</v>
       </c>
       <c r="M490" t="n">
-        <v>0.6609</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="N490" t="n">
         <v>0</v>
@@ -33207,7 +33208,7 @@
         </is>
       </c>
       <c r="F505" t="n">
-        <v>0.9721</v>
+        <v>0.9716</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
@@ -33215,7 +33216,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>0.9721</v>
+        <v>0.9716</v>
       </c>
       <c r="I505" t="n">
         <v>0</v>
@@ -33224,7 +33225,7 @@
         <v>0</v>
       </c>
       <c r="K505" t="n">
-        <v>0.0279</v>
+        <v>0.0284</v>
       </c>
       <c r="L505" t="n">
         <v>0</v>
@@ -33272,7 +33273,7 @@
         </is>
       </c>
       <c r="F506" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6946</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
@@ -33280,7 +33281,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6946</v>
       </c>
       <c r="I506" t="n">
         <v>0</v>
@@ -33289,7 +33290,7 @@
         <v>0</v>
       </c>
       <c r="K506" t="n">
-        <v>0.307</v>
+        <v>0.3054</v>
       </c>
       <c r="L506" t="n">
         <v>0</v>
@@ -33532,7 +33533,7 @@
         </is>
       </c>
       <c r="F510" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
@@ -33540,7 +33541,7 @@
         </is>
       </c>
       <c r="H510" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="I510" t="n">
         <v>0</v>
@@ -33561,7 +33562,7 @@
         <v>0</v>
       </c>
       <c r="O510" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="P510" t="inlineStr"/>
       <c r="Q510" t="inlineStr"/>
@@ -33597,7 +33598,7 @@
         </is>
       </c>
       <c r="F511" t="n">
-        <v>0.6222</v>
+        <v>0.6241</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
@@ -33605,7 +33606,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>0.6222</v>
+        <v>0.6241</v>
       </c>
       <c r="I511" t="n">
         <v>0</v>
@@ -33614,7 +33615,7 @@
         <v>0</v>
       </c>
       <c r="K511" t="n">
-        <v>0.3778</v>
+        <v>0.3759</v>
       </c>
       <c r="L511" t="n">
         <v>0</v>
@@ -34113,7 +34114,7 @@
         </is>
       </c>
       <c r="F519" t="n">
-        <v>0.8179</v>
+        <v>0.8144</v>
       </c>
       <c r="G519" t="inlineStr">
         <is>
@@ -34124,13 +34125,13 @@
         <v>0</v>
       </c>
       <c r="I519" t="n">
-        <v>0.1821</v>
+        <v>0.1856</v>
       </c>
       <c r="J519" t="n">
         <v>0</v>
       </c>
       <c r="K519" t="n">
-        <v>0.8179</v>
+        <v>0.8144</v>
       </c>
       <c r="L519" t="n">
         <v>0</v>
@@ -34304,7 +34305,7 @@
         </is>
       </c>
       <c r="F522" t="n">
-        <v>0.9946</v>
+        <v>0.9954</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
@@ -34315,13 +34316,13 @@
         <v>0</v>
       </c>
       <c r="I522" t="n">
-        <v>0.0054</v>
+        <v>0.0046</v>
       </c>
       <c r="J522" t="n">
         <v>0</v>
       </c>
       <c r="K522" t="n">
-        <v>0.9946</v>
+        <v>0.9954</v>
       </c>
       <c r="L522" t="n">
         <v>0</v>
@@ -34369,7 +34370,7 @@
         </is>
       </c>
       <c r="F523" t="n">
-        <v>0.8727</v>
+        <v>0.8717</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
@@ -34380,13 +34381,13 @@
         <v>0</v>
       </c>
       <c r="I523" t="n">
-        <v>0.1273</v>
+        <v>0.1283</v>
       </c>
       <c r="J523" t="n">
         <v>0</v>
       </c>
       <c r="K523" t="n">
-        <v>0.8727</v>
+        <v>0.8717</v>
       </c>
       <c r="L523" t="n">
         <v>0</v>
@@ -34434,7 +34435,7 @@
         </is>
       </c>
       <c r="F524" t="n">
-        <v>0.553</v>
+        <v>0.5538</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
@@ -34445,13 +34446,13 @@
         <v>0</v>
       </c>
       <c r="I524" t="n">
-        <v>0.553</v>
+        <v>0.5538</v>
       </c>
       <c r="J524" t="n">
         <v>0</v>
       </c>
       <c r="K524" t="n">
-        <v>0.447</v>
+        <v>0.4462</v>
       </c>
       <c r="L524" t="n">
         <v>0</v>
@@ -34694,7 +34695,7 @@
         </is>
       </c>
       <c r="F528" t="n">
-        <v>0.9792</v>
+        <v>0.9788</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
@@ -34705,13 +34706,13 @@
         <v>0</v>
       </c>
       <c r="I528" t="n">
-        <v>0.9792</v>
+        <v>0.9788</v>
       </c>
       <c r="J528" t="n">
         <v>0</v>
       </c>
       <c r="K528" t="n">
-        <v>0.0208</v>
+        <v>0.0212</v>
       </c>
       <c r="L528" t="n">
         <v>0</v>
@@ -34759,7 +34760,7 @@
         </is>
       </c>
       <c r="F529" t="n">
-        <v>0.9663</v>
+        <v>0.9687</v>
       </c>
       <c r="G529" t="inlineStr">
         <is>
@@ -34770,13 +34771,13 @@
         <v>0</v>
       </c>
       <c r="I529" t="n">
-        <v>0.0337</v>
+        <v>0.0313</v>
       </c>
       <c r="J529" t="n">
         <v>0</v>
       </c>
       <c r="K529" t="n">
-        <v>0.9663</v>
+        <v>0.9687</v>
       </c>
       <c r="L529" t="n">
         <v>0</v>
@@ -35084,7 +35085,7 @@
         </is>
       </c>
       <c r="F534" t="n">
-        <v>0.9818</v>
+        <v>0.9819</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
@@ -35092,7 +35093,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>0.9818</v>
+        <v>0.9819</v>
       </c>
       <c r="I534" t="n">
         <v>0</v>
@@ -35101,7 +35102,7 @@
         <v>0</v>
       </c>
       <c r="K534" t="n">
-        <v>0.0182</v>
+        <v>0.0181</v>
       </c>
       <c r="L534" t="n">
         <v>0</v>
@@ -35279,7 +35280,7 @@
         </is>
       </c>
       <c r="F537" t="n">
-        <v>0.9969</v>
+        <v>0.997</v>
       </c>
       <c r="G537" t="inlineStr">
         <is>
@@ -35290,13 +35291,13 @@
         <v>0</v>
       </c>
       <c r="I537" t="n">
-        <v>0.0031</v>
+        <v>0.003</v>
       </c>
       <c r="J537" t="n">
         <v>0</v>
       </c>
       <c r="K537" t="n">
-        <v>0.9969</v>
+        <v>0.997</v>
       </c>
       <c r="L537" t="n">
         <v>0</v>
@@ -35409,7 +35410,7 @@
         </is>
       </c>
       <c r="F539" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7456</v>
       </c>
       <c r="G539" t="inlineStr">
         <is>
@@ -35417,7 +35418,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>0.2555</v>
+        <v>0.2544</v>
       </c>
       <c r="I539" t="n">
         <v>0</v>
@@ -35426,7 +35427,7 @@
         <v>0</v>
       </c>
       <c r="K539" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7456</v>
       </c>
       <c r="L539" t="n">
         <v>0</v>
@@ -35474,7 +35475,7 @@
         </is>
       </c>
       <c r="F540" t="n">
-        <v>0.9594</v>
+        <v>0.9595</v>
       </c>
       <c r="G540" t="inlineStr">
         <is>
@@ -35485,13 +35486,13 @@
         <v>0</v>
       </c>
       <c r="I540" t="n">
-        <v>0.9594</v>
+        <v>0.9595</v>
       </c>
       <c r="J540" t="n">
         <v>0</v>
       </c>
       <c r="K540" t="n">
-        <v>0.0406</v>
+        <v>0.0405</v>
       </c>
       <c r="L540" t="n">
         <v>0</v>
@@ -35799,7 +35800,7 @@
         </is>
       </c>
       <c r="F545" t="n">
-        <v>0.5456</v>
+        <v>0.5458</v>
       </c>
       <c r="G545" t="inlineStr">
         <is>
@@ -35807,7 +35808,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>0.4544</v>
+        <v>0.4542</v>
       </c>
       <c r="I545" t="n">
         <v>0</v>
@@ -35816,7 +35817,7 @@
         <v>0</v>
       </c>
       <c r="K545" t="n">
-        <v>0.5456</v>
+        <v>0.5458</v>
       </c>
       <c r="L545" t="n">
         <v>0</v>
@@ -37615,7 +37616,7 @@
         </is>
       </c>
       <c r="F573" t="n">
-        <v>0.9837</v>
+        <v>0.9862</v>
       </c>
       <c r="G573" t="inlineStr">
         <is>
@@ -37623,7 +37624,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>0.0163</v>
+        <v>0.0138</v>
       </c>
       <c r="I573" t="n">
         <v>0</v>
@@ -37632,7 +37633,7 @@
         <v>0</v>
       </c>
       <c r="K573" t="n">
-        <v>0.9837</v>
+        <v>0.9862</v>
       </c>
       <c r="L573" t="n">
         <v>0</v>
@@ -37680,7 +37681,7 @@
         </is>
       </c>
       <c r="F574" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5064</v>
       </c>
       <c r="G574" t="inlineStr">
         <is>
@@ -37688,16 +37689,16 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>0.0286</v>
+        <v>0.0304</v>
       </c>
       <c r="I574" t="n">
-        <v>0.4588</v>
+        <v>0.4632</v>
       </c>
       <c r="J574" t="n">
         <v>0</v>
       </c>
       <c r="K574" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5064</v>
       </c>
       <c r="L574" t="n">
         <v>0</v>
@@ -38135,7 +38136,7 @@
         </is>
       </c>
       <c r="F581" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G581" t="inlineStr">
         <is>
@@ -38146,13 +38147,13 @@
         <v>0</v>
       </c>
       <c r="I581" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J581" t="n">
         <v>0</v>
       </c>
       <c r="K581" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="L581" t="n">
         <v>0</v>
@@ -38200,7 +38201,7 @@
         </is>
       </c>
       <c r="F582" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G582" t="inlineStr">
         <is>
@@ -38211,13 +38212,13 @@
         <v>0</v>
       </c>
       <c r="I582" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="J582" t="n">
         <v>0</v>
       </c>
       <c r="K582" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="L582" t="n">
         <v>0</v>
@@ -38785,7 +38786,7 @@
         </is>
       </c>
       <c r="F591" t="n">
-        <v>0.6878</v>
+        <v>0.6813</v>
       </c>
       <c r="G591" t="inlineStr">
         <is>
@@ -38796,13 +38797,13 @@
         <v>0</v>
       </c>
       <c r="I591" t="n">
-        <v>0.6878</v>
+        <v>0.6813</v>
       </c>
       <c r="J591" t="n">
         <v>0</v>
       </c>
       <c r="K591" t="n">
-        <v>0.3122</v>
+        <v>0.3187</v>
       </c>
       <c r="L591" t="n">
         <v>0</v>
@@ -39110,7 +39111,7 @@
         </is>
       </c>
       <c r="F596" t="n">
-        <v>0.9993</v>
+        <v>0.9983</v>
       </c>
       <c r="G596" t="inlineStr">
         <is>
@@ -39118,7 +39119,7 @@
         </is>
       </c>
       <c r="H596" t="n">
-        <v>0.9993</v>
+        <v>0.9983</v>
       </c>
       <c r="I596" t="n">
         <v>0</v>
@@ -39127,7 +39128,7 @@
         <v>0</v>
       </c>
       <c r="K596" t="n">
-        <v>0.0007</v>
+        <v>0.0017</v>
       </c>
       <c r="L596" t="n">
         <v>0</v>
@@ -39236,7 +39237,7 @@
         </is>
       </c>
       <c r="F598" t="n">
-        <v>0.6027</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="G598" t="inlineStr">
         <is>
@@ -39244,10 +39245,10 @@
         </is>
       </c>
       <c r="H598" t="n">
-        <v>0.6027</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="I598" t="n">
-        <v>0.3973</v>
+        <v>0.3977</v>
       </c>
       <c r="J598" t="n">
         <v>0</v>
@@ -39301,7 +39302,7 @@
         </is>
       </c>
       <c r="F599" t="n">
-        <v>0.9951</v>
+        <v>0.9938</v>
       </c>
       <c r="G599" t="inlineStr">
         <is>
@@ -39309,16 +39310,16 @@
         </is>
       </c>
       <c r="H599" t="n">
-        <v>0.9951</v>
+        <v>0.9938</v>
       </c>
       <c r="I599" t="n">
-        <v>0.0025</v>
+        <v>0.003</v>
       </c>
       <c r="J599" t="n">
         <v>0</v>
       </c>
       <c r="K599" t="n">
-        <v>0.0024</v>
+        <v>0.0032</v>
       </c>
       <c r="L599" t="n">
         <v>0</v>
@@ -39756,7 +39757,7 @@
         </is>
       </c>
       <c r="F606" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="G606" t="inlineStr">
         <is>
@@ -39764,7 +39765,7 @@
         </is>
       </c>
       <c r="H606" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="I606" t="n">
         <v>0</v>
@@ -39773,7 +39774,7 @@
         <v>0</v>
       </c>
       <c r="K606" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="L606" t="n">
         <v>0</v>
@@ -39951,7 +39952,7 @@
         </is>
       </c>
       <c r="F609" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="G609" t="inlineStr">
         <is>
@@ -39959,10 +39960,10 @@
         </is>
       </c>
       <c r="H609" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="I609" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J609" t="n">
         <v>0</v>
@@ -40666,7 +40667,7 @@
         </is>
       </c>
       <c r="F620" t="n">
-        <v>0.978</v>
+        <v>0.9775</v>
       </c>
       <c r="G620" t="inlineStr">
         <is>
@@ -40674,7 +40675,7 @@
         </is>
       </c>
       <c r="H620" t="n">
-        <v>0.978</v>
+        <v>0.9775</v>
       </c>
       <c r="I620" t="n">
         <v>0</v>
@@ -40683,7 +40684,7 @@
         <v>0</v>
       </c>
       <c r="K620" t="n">
-        <v>0.022</v>
+        <v>0.0225</v>
       </c>
       <c r="L620" t="n">
         <v>0</v>
@@ -40731,7 +40732,7 @@
         </is>
       </c>
       <c r="F621" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G621" t="inlineStr">
         <is>
@@ -40742,13 +40743,13 @@
         <v>0</v>
       </c>
       <c r="I621" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J621" t="n">
         <v>0</v>
       </c>
       <c r="K621" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="L621" t="n">
         <v>0</v>
@@ -41117,7 +41118,7 @@
         </is>
       </c>
       <c r="F627" t="n">
-        <v>0.9744</v>
+        <v>0.9739</v>
       </c>
       <c r="G627" t="inlineStr">
         <is>
@@ -41125,7 +41126,7 @@
         </is>
       </c>
       <c r="H627" t="n">
-        <v>0.0256</v>
+        <v>0.0261</v>
       </c>
       <c r="I627" t="n">
         <v>0</v>
@@ -41134,7 +41135,7 @@
         <v>0</v>
       </c>
       <c r="K627" t="n">
-        <v>0.9744</v>
+        <v>0.9739</v>
       </c>
       <c r="L627" t="n">
         <v>0</v>
@@ -41572,7 +41573,7 @@
         </is>
       </c>
       <c r="F634" t="n">
-        <v>0.9432</v>
+        <v>0.9435</v>
       </c>
       <c r="G634" t="inlineStr">
         <is>
@@ -41583,13 +41584,13 @@
         <v>0</v>
       </c>
       <c r="I634" t="n">
-        <v>0.9432</v>
+        <v>0.9435</v>
       </c>
       <c r="J634" t="n">
         <v>0</v>
       </c>
       <c r="K634" t="n">
-        <v>0.0568</v>
+        <v>0.0565</v>
       </c>
       <c r="L634" t="n">
         <v>0</v>
@@ -41962,7 +41963,7 @@
         </is>
       </c>
       <c r="F640" t="n">
-        <v>0.9996</v>
+        <v>0.9989</v>
       </c>
       <c r="G640" t="inlineStr">
         <is>
@@ -41970,7 +41971,7 @@
         </is>
       </c>
       <c r="H640" t="n">
-        <v>0.9996</v>
+        <v>0.9989</v>
       </c>
       <c r="I640" t="n">
         <v>0</v>
@@ -41979,7 +41980,7 @@
         <v>0</v>
       </c>
       <c r="K640" t="n">
-        <v>0.0004</v>
+        <v>0.0011</v>
       </c>
       <c r="L640" t="n">
         <v>0</v>
@@ -42027,7 +42028,7 @@
         </is>
       </c>
       <c r="F641" t="n">
-        <v>0.8488</v>
+        <v>0.8447</v>
       </c>
       <c r="G641" t="inlineStr">
         <is>
@@ -42035,7 +42036,7 @@
         </is>
       </c>
       <c r="H641" t="n">
-        <v>0.1512</v>
+        <v>0.1553</v>
       </c>
       <c r="I641" t="n">
         <v>0</v>
@@ -42044,7 +42045,7 @@
         <v>0</v>
       </c>
       <c r="K641" t="n">
-        <v>0.8488</v>
+        <v>0.8447</v>
       </c>
       <c r="L641" t="n">
         <v>0</v>
@@ -42157,7 +42158,7 @@
         </is>
       </c>
       <c r="F643" t="n">
-        <v>0.7249</v>
+        <v>0.7205</v>
       </c>
       <c r="G643" t="inlineStr">
         <is>
@@ -42165,10 +42166,10 @@
         </is>
       </c>
       <c r="H643" t="n">
-        <v>0.2751</v>
+        <v>0.2795</v>
       </c>
       <c r="I643" t="n">
-        <v>0.7249</v>
+        <v>0.7205</v>
       </c>
       <c r="J643" t="n">
         <v>0</v>
@@ -42222,7 +42223,7 @@
         </is>
       </c>
       <c r="F644" t="n">
-        <v>0.9994</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G644" t="inlineStr">
         <is>
@@ -42230,7 +42231,7 @@
         </is>
       </c>
       <c r="H644" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0005</v>
       </c>
       <c r="I644" t="n">
         <v>0</v>
@@ -42239,7 +42240,7 @@
         <v>0</v>
       </c>
       <c r="K644" t="n">
-        <v>0.9994</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="L644" t="n">
         <v>0</v>
@@ -42677,7 +42678,7 @@
         </is>
       </c>
       <c r="F651" t="n">
-        <v>0.9987</v>
+        <v>0.9981</v>
       </c>
       <c r="G651" t="inlineStr">
         <is>
@@ -42685,10 +42686,10 @@
         </is>
       </c>
       <c r="H651" t="n">
-        <v>0.9987</v>
+        <v>0.9981</v>
       </c>
       <c r="I651" t="n">
-        <v>0.0013</v>
+        <v>0.0019</v>
       </c>
       <c r="J651" t="n">
         <v>0</v>
@@ -42742,32 +42743,32 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>popular_vote_proj</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>median_seats</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>mean_seats</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>p10_seats</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>p90_seats</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>majority_prob</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>largest_party_prob</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -42788,25 +42789,25 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="D2" t="n">
         <v>144</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>145.1</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>132</v>
       </c>
-      <c r="F2" t="n">
-        <v>160</v>
-      </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="3">
@@ -42821,19 +42822,19 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>0.1999</v>
+      </c>
+      <c r="D3" t="n">
         <v>95</v>
       </c>
-      <c r="D3" t="n">
-        <v>96.7</v>
-      </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F3" t="n">
+        <v>81</v>
+      </c>
+      <c r="G3" t="n">
         <v>114</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -42854,19 +42855,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>76</v>
+        <v>0.1266</v>
       </c>
       <c r="D4" t="n">
         <v>76</v>
       </c>
       <c r="E4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F4" t="n">
         <v>75</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>77</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -42887,25 +42888,25 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>0.2264</v>
+      </c>
+      <c r="D5" t="n">
         <v>230</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>228.6</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>212</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>244</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
-        <v>0.9999</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="6">
@@ -42920,19 +42921,19 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="D6" t="n">
         <v>15</v>
       </c>
-      <c r="D6" t="n">
-        <v>15.1</v>
-      </c>
       <c r="E6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" t="n">
         <v>14</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>17</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -42953,19 +42954,19 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="D7" t="n">
         <v>48</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>46.8</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>44</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>49</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -42986,7 +42987,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>0.0081</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -42998,7 +42999,7 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -43019,19 +43020,19 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="D9" t="n">
+        <v>19</v>
+      </c>
+      <c r="E9" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F9" t="n">
         <v>18</v>
       </c>
-      <c r="D9" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="E9" t="n">
-        <v>18</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>21</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -43052,7 +43053,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>0.0064</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
@@ -43064,7 +43065,7 @@
         <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -43085,7 +43086,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>0.0069</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
@@ -43097,7 +43098,7 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -43118,7 +43119,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0.0041</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -43130,7 +43131,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -43151,7 +43152,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>0.0032</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -43163,7 +43164,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -43184,7 +43185,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0.0031</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -43196,7 +43197,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -43217,7 +43218,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0.0027</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -43229,7 +43230,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -43249,6 +43250,294 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>party_display</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>projected_vote_share</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>projected_vote_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.2170326918208444</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>con</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1999091385951484</v>
+      </c>
+      <c r="D3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ld</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Liberal Democrat</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1265763465677524</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>reform</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Reform UK</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2263530324396771</v>
+      </c>
+      <c r="D5" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1185301618663843</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>snp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SNP</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.03187736687126912</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Plaid Cymru</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.008105334522277763</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>oth</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.04513170920448195</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ni_dup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DUP</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.006421096567901008</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ni_sf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sinn Féin</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.006917722928008439</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ni_alliance</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Alliance</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.004075295506547149</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ni_sdlp</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SDLP</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.003188477632229926</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ni_uup</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>UUP</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.003142796182483787</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ni_tuv</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TUV</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.002738829294994254</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -44082,7 +44371,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>South Derbyshire</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -44097,7 +44386,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>oth</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -44107,7 +44396,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rossendale and Darwen</t>
+          <t>South Derbyshire</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -44132,7 +44421,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rother Valley</t>
+          <t>Rossendale and Darwen</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -44157,7 +44446,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Rother Valley</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -44182,7 +44471,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Scarborough and Whitby</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -44207,7 +44496,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Scarborough and Whitby</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -44232,7 +44521,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Corby and East Northamptonshire</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -44257,7 +44546,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Coventry North West</t>
+          <t>Corby and East Northamptonshire</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -44282,7 +44571,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cramlington and Killingworth</t>
+          <t>Coventry North West</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -44307,7 +44596,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Crewe and Nantwich</t>
+          <t>Cramlington and Killingworth</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -44332,7 +44621,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Chatham and Aylesford</t>
+          <t>Crewe and Nantwich</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -44357,7 +44646,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Chatham and Aylesford</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -44382,7 +44671,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>City of Durham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -44407,7 +44696,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Burton and Uttoxeter</t>
+          <t>City of Durham</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -44432,7 +44721,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bury St Edmunds and Stowmarket</t>
+          <t>Burton and Uttoxeter</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -44457,12 +44746,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Caerphilly</t>
+          <t>Bury St Edmunds and Stowmarket</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -44482,12 +44771,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Camborne and Redruth</t>
+          <t>Caerphilly</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -44507,7 +44796,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cannock Chase</t>
+          <t>Camborne and Redruth</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -44532,7 +44821,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Cannock Chase</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -44557,7 +44846,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Castle Point</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -44567,7 +44856,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -44582,22 +44871,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Central Ayrshire</t>
+          <t>Castle Point</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -44607,12 +44896,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bristol East</t>
+          <t>Central Ayrshire</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -44622,7 +44911,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -44632,7 +44921,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bristol South</t>
+          <t>Bristol East</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -44657,7 +44946,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Broxtowe</t>
+          <t>Bristol South</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -44672,7 +44961,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>green</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -44682,7 +44971,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Broxtowe</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -44707,12 +44996,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Edinburgh South West</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -44722,7 +45011,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -44732,12 +45021,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Erewash</t>
+          <t>Edinburgh South West</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -44747,7 +45036,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -44757,12 +45046,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Erewash</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -44772,7 +45061,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -44782,12 +45071,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Folkestone and Hythe</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -44797,7 +45086,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -44807,7 +45096,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Easington</t>
+          <t>Farnham and Bordon</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -44817,12 +45106,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -44832,12 +45121,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>East Kilbride and Strathaven</t>
+          <t>Folkestone and Hythe</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -44847,7 +45136,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -44857,12 +45146,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>East Renfrewshire</t>
+          <t>Earley and Woodley</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -44872,7 +45161,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -44882,12 +45171,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Edinburgh East and Musselburgh</t>
+          <t>Easington</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -44897,7 +45186,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -44907,7 +45196,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Edinburgh North and Leith</t>
+          <t>East Kilbride and Strathaven</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -44932,12 +45221,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Doncaster Central</t>
+          <t>East Renfrewshire</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -44947,7 +45236,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -44957,12 +45246,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Doncaster East and the Isle of Axholme</t>
+          <t>Edinburgh East and Musselburgh</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -44972,7 +45261,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -44982,12 +45271,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Dover and Deal</t>
+          <t>Edinburgh North and Leith</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -44997,7 +45286,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -45007,7 +45296,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Dudley</t>
+          <t>Doncaster Central</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -45032,22 +45321,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dumfries and Galloway</t>
+          <t>Doncaster East and the Isle of Axholme</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -45057,12 +45346,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cumbernauld and Kirkintilloch</t>
+          <t>Dover and Deal</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -45072,7 +45361,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -45082,7 +45371,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Dartford</t>
+          <t>Dudley</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -45107,22 +45396,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Derby North</t>
+          <t>Dumfries and Galloway</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -45132,12 +45421,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Derby South</t>
+          <t>Cumbernauld and Kirkintilloch</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -45147,7 +45436,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -45157,7 +45446,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Derbyshire Dales</t>
+          <t>Dartford</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -45172,7 +45461,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -45182,7 +45471,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Rayleigh and Wickford</t>
+          <t>Derby North</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -45192,7 +45481,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -45207,7 +45496,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Reading West and Mid Berkshire</t>
+          <t>Derby South</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -45222,7 +45511,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -45232,7 +45521,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Redcar</t>
+          <t>Derbyshire Dales</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -45247,7 +45536,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -45257,7 +45546,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Redditch</t>
+          <t>Rayleigh and Wickford</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -45267,7 +45556,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -45282,12 +45571,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Rhondda and Ogmore</t>
+          <t>Reading West and Mid Berkshire</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -45297,7 +45586,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -45307,7 +45596,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Rochester and Strood</t>
+          <t>Redcar</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -45332,7 +45621,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Plymouth Moor View</t>
+          <t>Redditch</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -45357,12 +45646,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Pontefract, Castleford and Knottingley</t>
+          <t>Rhondda and Ogmore</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -45382,12 +45671,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Pontypridd</t>
+          <t>Rochester and Strood</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -45407,7 +45696,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Rawmarsh and Conisbrough</t>
+          <t>Plymouth Moor View</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -45432,7 +45721,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Nuneaton</t>
+          <t>Pontefract, Castleford and Knottingley</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -45457,12 +45746,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Oldham East and Saddleworth</t>
+          <t>Pontypridd</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -45482,7 +45771,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ossett and Denby Dale</t>
+          <t>Rawmarsh and Conisbrough</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -45507,12 +45796,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Paisley and Renfrewshire North</t>
+          <t>Nuneaton</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -45522,7 +45811,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -45532,12 +45821,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Paisley and Renfrewshire South</t>
+          <t>Oldham East and Saddleworth</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -45547,7 +45836,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -45557,7 +45846,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Penistone and Stocksbridge</t>
+          <t>Ossett and Denby Dale</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -45582,12 +45871,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>North Warwickshire and Bedworth</t>
+          <t>Paisley and Renfrewshire North</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -45597,7 +45886,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -45607,12 +45896,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>North West Cambridgeshire</t>
+          <t>Paisley and Renfrewshire South</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -45622,7 +45911,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -45632,7 +45921,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>North West Leicestershire</t>
+          <t>Penistone and Stocksbridge</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -45657,7 +45946,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Northampton South</t>
+          <t>North Warwickshire and Bedworth</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -45682,7 +45971,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Nottingham North and Kimberley</t>
+          <t>North West Cambridgeshire</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -45707,7 +45996,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>North West Leicestershire</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -45717,7 +46006,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -45732,7 +46021,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>Northampton South</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -45757,7 +46046,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Hexham</t>
+          <t>Nottingham North and Kimberley</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -45772,7 +46061,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -45782,7 +46071,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Heywood and Middleton North</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -45792,7 +46081,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -45807,7 +46096,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Hornchurch and Upminster</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45817,7 +46106,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -45832,7 +46121,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Great Grimsby and Cleethorpes</t>
+          <t>Hexham</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45847,7 +46136,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -45857,7 +46146,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Halesowen</t>
+          <t>Heywood and Middleton North</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45882,7 +46171,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Hornchurch and Upminster</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -45892,7 +46181,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -45907,7 +46196,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Great Grimsby and Cleethorpes</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -45932,7 +46221,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Halesowen</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -45957,7 +46246,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Harwich and North Essex</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -45967,7 +46256,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -45982,12 +46271,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Glasgow South West</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -45997,7 +46286,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -46007,12 +46296,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Glasgow West</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -46022,7 +46311,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -46032,22 +46321,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Glenrothes and Mid Fife</t>
+          <t>Harwich and North Essex</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -46057,22 +46346,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Godalming and Ash</t>
+          <t>Glasgow South West</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -46082,7 +46371,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Gordon and Buchan</t>
+          <t>Glasgow West</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -46092,7 +46381,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -46107,22 +46396,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Gainsborough</t>
+          <t>Glenrothes and Mid Fife</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -46132,7 +46421,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Gateshead Central and Whickham</t>
+          <t>Godalming and Ash</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -46142,12 +46431,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -46157,22 +46446,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Gillingham and Rainham</t>
+          <t>Gordon and Buchan</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -46182,22 +46471,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Glasgow East</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -46207,12 +46496,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Glasgow North</t>
+          <t>Gateshead Central and Whickham</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -46222,7 +46511,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -46232,12 +46521,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Glasgow North East</t>
+          <t>Gillingham and Rainham</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -46247,7 +46536,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -46257,7 +46546,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Glasgow South</t>
+          <t>Glasgow East</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -46282,12 +46571,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Llanelli</t>
+          <t>Glasgow North</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -46297,7 +46586,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -46307,12 +46596,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Loughborough</t>
+          <t>Glasgow North East</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -46322,7 +46611,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -46332,22 +46621,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Louth and Horncastle</t>
+          <t>Glasgow South</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -46357,12 +46646,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Lowestoft</t>
+          <t>Llanelli</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -46382,7 +46671,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Luton South and South Bedfordshire</t>
+          <t>Loughborough</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -46397,7 +46686,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>oth</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -46407,7 +46696,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Makerfield</t>
+          <t>Louth and Horncastle</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -46417,7 +46706,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -46432,7 +46721,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Maldon</t>
+          <t>Lowestoft</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -46442,7 +46731,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -46457,7 +46746,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Leeds Central and Headingley</t>
+          <t>Luton South and South Bedfordshire</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -46472,7 +46761,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>oth</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -46482,7 +46771,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Leeds East</t>
+          <t>Makerfield</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -46507,7 +46796,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Leeds South West and Morley</t>
+          <t>Maldon</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -46517,7 +46806,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -46532,7 +46821,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Leigh and Atherton</t>
+          <t>Leeds Central and Headingley</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -46547,7 +46836,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>green</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -46557,7 +46846,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Lichfield</t>
+          <t>Leeds East</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -46582,7 +46871,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Leeds South West and Morley</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -46607,12 +46896,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Leigh and Atherton</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -46622,7 +46911,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -46632,7 +46921,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Isle of Wight East</t>
+          <t>Lichfield</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -46642,12 +46931,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -46657,7 +46946,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Jarrow and Gateshead East</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -46682,12 +46971,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -46697,7 +46986,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -46707,22 +46996,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kilmarnock and Loudoun</t>
+          <t>Isle of Wight East</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>green</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -46732,7 +47021,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Kingston upon Hull East</t>
+          <t>Jarrow and Gateshead East</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -46757,7 +47046,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kingston upon Hull North and Cottingham</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -46782,12 +47071,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Kingston upon Hull West and Haltemprice</t>
+          <t>Kilmarnock and Loudoun</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -46797,7 +47086,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -46807,7 +47096,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Houghton and Sunderland South</t>
+          <t>Kingston upon Hull East</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -46832,7 +47121,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Huddersfield</t>
+          <t>Kingston upon Hull North and Cottingham</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -46847,7 +47136,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -46857,7 +47146,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Hyndburn</t>
+          <t>Kingston upon Hull West and Haltemprice</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -46882,7 +47171,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ilford North</t>
+          <t>Houghton and Sunderland South</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -46897,7 +47186,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>oth</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -46907,12 +47196,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Inverclyde and Renfrewshire West</t>
+          <t>Huddersfield</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -46922,7 +47211,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>green</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -46932,22 +47221,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Inverness, Skye and West Ross-shire</t>
+          <t>Hyndburn</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -46957,12 +47246,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>North Ayrshire and Arran</t>
+          <t>Ilford North</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -46972,7 +47261,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>oth</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -46982,22 +47271,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>North Down</t>
+          <t>Inverclyde and Renfrewshire West</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Northern Ireland</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>oth</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ni_tuv</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -47007,22 +47296,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>North Durham</t>
+          <t>Inverness, Skye and West Ross-shire</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -47032,12 +47321,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>North Northumberland</t>
+          <t>North Ayrshire and Arran</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -47047,7 +47336,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -47057,22 +47346,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>North Somerset</t>
+          <t>North Down</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Northern Ireland</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>oth</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>ni_tuv</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -47082,7 +47371,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Newcastle upon Tyne Central and West</t>
+          <t>North Durham</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -47107,7 +47396,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Newcastle upon Tyne East and Wallsend</t>
+          <t>North Northumberland</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -47132,7 +47421,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Newcastle-under-Lyme</t>
+          <t>North Somerset</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -47147,7 +47436,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -47157,12 +47446,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Newport East</t>
+          <t>Newcastle upon Tyne Central and West</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -47182,12 +47471,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Newport West and Islwyn</t>
+          <t>Newcastle upon Tyne East and Wallsend</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -47207,7 +47496,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Newton Aycliffe and Spennymoor</t>
+          <t>Newcastle-under-Lyme</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -47232,12 +47521,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Normanton and Hemsworth</t>
+          <t>Newport East</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -47257,22 +47546,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>North Antrim</t>
+          <t>Newport West and Islwyn</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Northern Ireland</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ni_tuv</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ni_dup</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -47282,7 +47571,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Middlesbrough and Thornaby East</t>
+          <t>Newton Aycliffe and Spennymoor</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -47307,7 +47596,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Middlesbrough South and East Cleveland</t>
+          <t>Normanton and Hemsworth</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -47322,7 +47611,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -47332,22 +47621,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Montgomeryshire and Glyndŵr</t>
+          <t>North Antrim</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>Northern Ireland</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>ni_tuv</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>ni_dup</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -47357,12 +47646,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Neath and Swansea East</t>
+          <t>Middlesbrough and Thornaby East</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -47382,7 +47671,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Mansfield</t>
+          <t>Middlesbrough South and East Cleveland</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -47397,7 +47686,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -47407,7 +47696,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Merthyr Tydfil and Aberdare</t>
+          <t>Montgomeryshire and Glyndŵr</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -47432,12 +47721,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Wellingborough and Rushden</t>
+          <t>Motherwell, Wishaw and Carluke</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -47447,7 +47736,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -47457,22 +47746,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>West Aberdeenshire and Kincardine</t>
+          <t>Neath and Swansea East</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -47482,7 +47771,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>West Bromwich</t>
+          <t>Mansfield</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -47507,12 +47796,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>West Dunbartonshire</t>
+          <t>Merthyr Tydfil and Aberdare</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -47522,7 +47811,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -47532,7 +47821,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Weston-super-Mare</t>
+          <t>Wellingborough and Rushden</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -47557,22 +47846,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Thurrock</t>
+          <t>West Aberdeenshire and Kincardine</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -47582,7 +47871,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Tipton and Wednesbury</t>
+          <t>West Bromwich</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -47607,12 +47896,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Torfaen</t>
+          <t>West Dunbartonshire</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -47622,7 +47911,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -47632,7 +47921,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Wakefield and Rothwell</t>
+          <t>West Suffolk</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -47642,7 +47931,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -47657,7 +47946,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Walsall and Bloxwich</t>
+          <t>Weston-super-Mare</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -47682,7 +47971,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Warrington North</t>
+          <t>The Wrekin</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -47692,7 +47981,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -47707,7 +47996,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Washington and Gateshead South</t>
+          <t>Thurrock</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -47732,7 +48021,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Stoke-on-Trent South</t>
+          <t>Tipton and Wednesbury</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -47757,12 +48046,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Stourbridge</t>
+          <t>Torfaen</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -47782,7 +48071,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sunderland Central</t>
+          <t>Wakefield and Rothwell</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -47807,7 +48096,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Walsall and Bloxwich</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -47832,7 +48121,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Telford</t>
+          <t>Warrington North</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -47857,7 +48146,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Washington and Gateshead South</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -47882,7 +48171,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Staffordshire Moorlands</t>
+          <t>Stoke-on-Trent South</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -47892,7 +48181,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -47907,7 +48196,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Stalybridge and Hyde</t>
+          <t>Stourbridge</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -47932,7 +48221,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Sunderland Central</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -47957,12 +48246,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Stirling and Strathallan</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -47972,7 +48261,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -47982,7 +48271,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Stockton North</t>
+          <t>Telford</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -48007,7 +48296,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Stoke-on-Trent Central</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -48032,7 +48321,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Stoke-on-Trent North</t>
+          <t>Staffordshire Moorlands</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -48042,7 +48331,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -48057,7 +48346,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Bradford West</t>
+          <t>Stalybridge and Hyde</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -48072,7 +48361,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>oth</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -48082,7 +48371,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -48092,7 +48381,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -48107,22 +48396,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Brentwood and Ongar</t>
+          <t>Stirling and Strathallan</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -48132,12 +48421,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Bridgend</t>
+          <t>Stockton North</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -48157,7 +48446,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Bridgwater</t>
+          <t>Stoke-on-Trent Central</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -48167,7 +48456,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -48182,7 +48471,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Bridlington and The Wolds</t>
+          <t>Stoke-on-Trent North</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -48192,7 +48481,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -48207,7 +48496,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Brigg and Immingham</t>
+          <t>Bradford West</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -48217,12 +48506,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>oth</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -48232,7 +48521,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Bolsover</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -48242,7 +48531,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -48257,7 +48546,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Bolton North East</t>
+          <t>Brentwood and Ongar</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -48267,7 +48556,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -48282,12 +48571,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Bolton South and Walkden</t>
+          <t>Bridgend</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -48307,7 +48596,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Bolton West</t>
+          <t>Bridgwater</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -48317,7 +48606,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -48332,7 +48621,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Bradford South</t>
+          <t>Bridlington and The Wolds</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -48342,7 +48631,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -48357,7 +48646,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Birmingham Yardley</t>
+          <t>Brigg and Immingham</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -48367,12 +48656,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>oth</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -48382,7 +48671,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Bishop Auckland</t>
+          <t>Bolsover</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -48407,7 +48696,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Blackpool North and Fleetwood</t>
+          <t>Bolton North East</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -48432,7 +48721,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Blackpool South</t>
+          <t>Bolton South and Walkden</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -48457,7 +48746,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Blaydon and Consett</t>
+          <t>Bolton West</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -48482,7 +48771,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Blyth and Ashington</t>
+          <t>Bradford South</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -48507,7 +48796,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Bexleyheath and Crayford</t>
+          <t>Birmingham Yardley</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -48522,7 +48811,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>oth</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -48532,7 +48821,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Birmingham Erdington</t>
+          <t>Bishop Auckland</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -48557,7 +48846,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Birmingham Hall Green and Moseley</t>
+          <t>Blackpool North and Fleetwood</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -48572,7 +48861,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>oth</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -48582,7 +48871,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Birmingham Hodge Hill and Solihull North</t>
+          <t>Blackpool South</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -48607,7 +48896,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Birmingham Northfield</t>
+          <t>Blaydon and Consett</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -48632,7 +48921,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>The Wrekin</t>
+          <t>Blyth and Ashington</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -48642,7 +48931,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -48651,13 +48940,13 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>West Suffolk</t>
+          <t>Bognor Regis and Littlehampton</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -48676,13 +48965,13 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Bournemouth West</t>
+          <t>Bexleyheath and Crayford</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -48701,13 +48990,13 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Bognor Regis and Littlehampton</t>
+          <t>Birmingham Erdington</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -48717,7 +49006,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -48726,18 +49015,18 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Motherwell, Wishaw and Carluke</t>
+          <t>Birmingham Hall Green and Moseley</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -48747,17 +49036,17 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>oth</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Slough</t>
+          <t>Birmingham Hodge Hill and Solihull North</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -48772,17 +49061,17 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>oth</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Farnham and Bordon</t>
+          <t>Birmingham Northfield</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -48792,27 +49081,27 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Earley and Woodley</t>
+          <t>Coatbridge and Bellshill</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -48822,7 +49111,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -48851,13 +49140,13 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Peterborough</t>
+          <t>Portsmouth North</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -48872,17 +49161,17 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Portsmouth North</t>
+          <t>Gravesham</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -48901,13 +49190,13 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Gravesham</t>
+          <t>Bournemouth West</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -48926,18 +49215,18 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Coatbridge and Bellshill</t>
+          <t>Peterborough</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -48947,11 +49236,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>0.9997</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="229">
@@ -48976,13 +49265,13 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Dagenham and Rainham</t>
+          <t>Colne Valley</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -49001,18 +49290,18 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -49022,11 +49311,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>oth</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>0.9994</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="232">
@@ -49051,13 +49340,13 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>0.9994</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Colne Valley</t>
+          <t>Dagenham and Rainham</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -49076,18 +49365,18 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>0.9993</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Coventry East</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -49101,7 +49390,7 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>0.999</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="235">
@@ -49126,13 +49415,13 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>0.999</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Oldham West, Chadderton and Royton</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -49151,13 +49440,13 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>0.9986</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Oldham West, Chadderton and Royton</t>
+          <t>Coventry East</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -49172,11 +49461,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>oth</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>0.9986</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="238">
@@ -49201,7 +49490,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>0.9986</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="239">
@@ -49226,7 +49515,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9987</v>
       </c>
     </row>
     <row r="240">
@@ -49251,13 +49540,13 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Brighton Kemptown and Peacehaven</t>
+          <t>Norwich North</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -49272,17 +49561,17 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>0.9981</v>
+        <v>0.9976</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Norwich North</t>
+          <t>Southend West and Leigh</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -49301,13 +49590,13 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>0.9972</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Southend West and Leigh</t>
+          <t>Brighton Kemptown and Peacehaven</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -49322,11 +49611,11 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>green</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>0.9969</v>
+        <v>0.9968</v>
       </c>
     </row>
     <row r="244">
@@ -49357,7 +49646,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Mid Cheshire</t>
+          <t>South Holland and The Deepings</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -49367,7 +49656,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -49376,13 +49665,13 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>0.9949</v>
+        <v>0.9954</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>South Holland and The Deepings</t>
+          <t>Mid Cheshire</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -49392,7 +49681,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -49401,13 +49690,13 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>0.9946</v>
+        <v>0.9954</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Welwyn Hatfield</t>
+          <t>East Thanet</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -49422,11 +49711,11 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>0.9941</v>
+        <v>0.9949</v>
       </c>
     </row>
     <row r="248">
@@ -49451,13 +49740,13 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>0.994</v>
+        <v>0.9947</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>East Thanet</t>
+          <t>Welwyn Hatfield</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -49472,11 +49761,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>0.9935</v>
+        <v>0.9941</v>
       </c>
     </row>
     <row r="250">
@@ -49501,7 +49790,7 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>0.9929</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="251">
@@ -49526,7 +49815,7 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>0.9928</v>
+        <v>0.9926</v>
       </c>
     </row>
     <row r="252">
@@ -49551,43 +49840,43 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>0.9901</v>
+        <v>0.9911</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Dumfriesshire, Clydesdale and Tweeddale</t>
+          <t>Darlington</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>0.9892</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Darlington</t>
+          <t>Clwyd North</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -49601,32 +49890,32 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>0.9889</v>
+        <v>0.9897</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Ribble Valley</t>
+          <t>Dumfriesshire, Clydesdale and Tweeddale</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>0.9885</v>
+        <v>0.9893</v>
       </c>
     </row>
     <row r="256">
@@ -49651,18 +49940,18 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>0.9883</v>
+        <v>0.9888</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Clwyd North</t>
+          <t>Ribble Valley</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -49672,11 +49961,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>0.9866</v>
+        <v>0.9883999999999999</v>
       </c>
     </row>
     <row r="258">
@@ -49701,7 +49990,7 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>0.986</v>
+        <v>0.9872</v>
       </c>
     </row>
     <row r="259">
@@ -49726,7 +50015,7 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>0.9837</v>
+        <v>0.9862</v>
       </c>
     </row>
     <row r="260">
@@ -49751,7 +50040,7 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>0.9825</v>
+        <v>0.9848</v>
       </c>
     </row>
     <row r="261">
@@ -49776,7 +50065,7 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9822</v>
       </c>
     </row>
     <row r="262">
@@ -49801,7 +50090,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9813</v>
       </c>
     </row>
     <row r="263">
@@ -49826,13 +50115,13 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>0.9774</v>
+        <v>0.9798</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Romsey and Southampton North</t>
+          <t>Central Suffolk and North Ipswich</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -49847,17 +50136,17 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Central Suffolk and North Ipswich</t>
+          <t>Romsey and Southampton North</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -49872,22 +50161,22 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>0.9754</v>
+        <v>0.9769</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Monmouthshire</t>
+          <t>Whitehaven and Workington</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -49897,22 +50186,22 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>0.9748</v>
+        <v>0.9739</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Whitehaven and Workington</t>
+          <t>Monmouthshire</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -49922,11 +50211,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>0.9744</v>
+        <v>0.9731</v>
       </c>
     </row>
     <row r="268">
@@ -49951,13 +50240,13 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>0.9663</v>
+        <v>0.9687</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Buckingham and Bletchley</t>
+          <t>Morecambe and Lunesdale</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -49972,17 +50261,17 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>0.965</v>
+        <v>0.9648</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Morecambe and Lunesdale</t>
+          <t>Buckingham and Bletchley</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -49997,11 +50286,11 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>0.9648</v>
+        <v>0.9646</v>
       </c>
     </row>
     <row r="271">
@@ -50026,7 +50315,7 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>0.9644</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="272">
@@ -50051,7 +50340,7 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>0.9575</v>
+        <v>0.9611</v>
       </c>
     </row>
     <row r="273">
@@ -50076,7 +50365,7 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>0.9559</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="274">
@@ -50101,7 +50390,7 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>0.9546</v>
+        <v>0.9528</v>
       </c>
     </row>
     <row r="275">
@@ -50126,7 +50415,7 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>0.9516</v>
+        <v>0.9522</v>
       </c>
     </row>
     <row r="276">
@@ -50151,7 +50440,7 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>0.9512</v>
+        <v>0.9510999999999999</v>
       </c>
     </row>
     <row r="277">
@@ -50176,7 +50465,7 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>0.9425</v>
+        <v>0.9404</v>
       </c>
     </row>
     <row r="278">
@@ -50201,13 +50490,13 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>0.9344</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Northampton North</t>
+          <t>Hertford and Stortford</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -50226,7 +50515,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>0.9292</v>
+        <v>0.9274</v>
       </c>
     </row>
     <row r="280">
@@ -50251,13 +50540,13 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>0.9273</v>
+        <v>0.9251</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Hertford and Stortford</t>
+          <t>Northampton North</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -50276,7 +50565,7 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>0.9264</v>
+        <v>0.9242</v>
       </c>
     </row>
     <row r="282">
@@ -50301,7 +50590,7 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>0.9123</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="283">
@@ -50326,7 +50615,7 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>0.8948</v>
+        <v>0.8919</v>
       </c>
     </row>
     <row r="284">
@@ -50351,7 +50640,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>0.8834</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="285">
@@ -50376,7 +50665,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>0.8747</v>
+        <v>0.8744</v>
       </c>
     </row>
     <row r="286">
@@ -50401,13 +50690,13 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>0.8727</v>
+        <v>0.8717</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Worcester</t>
+          <t>East Hampshire</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -50417,22 +50706,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>0.8488</v>
+        <v>0.8472</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>East Hampshire</t>
+          <t>Worcester</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -50442,16 +50731,16 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>0.8455</v>
+        <v>0.8447</v>
       </c>
     </row>
     <row r="289">
@@ -50476,7 +50765,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>0.8213</v>
+        <v>0.8173</v>
       </c>
     </row>
     <row r="290">
@@ -50501,7 +50790,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>0.8179</v>
+        <v>0.8144</v>
       </c>
     </row>
     <row r="291">
@@ -50526,7 +50815,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>0.7923</v>
+        <v>0.7881</v>
       </c>
     </row>
     <row r="292">
@@ -50551,7 +50840,7 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>0.7857</v>
+        <v>0.7835</v>
       </c>
     </row>
     <row r="293">
@@ -50576,7 +50865,7 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>0.7722</v>
+        <v>0.7639</v>
       </c>
     </row>
     <row r="294">
@@ -50601,7 +50890,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>0.763</v>
+        <v>0.7566000000000001</v>
       </c>
     </row>
     <row r="295">
@@ -50626,7 +50915,7 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>0.755</v>
+        <v>0.7511</v>
       </c>
     </row>
     <row r="296">
@@ -50651,7 +50940,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7456</v>
       </c>
     </row>
     <row r="297">
@@ -50676,7 +50965,7 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>0.7252</v>
+        <v>0.7208</v>
       </c>
     </row>
     <row r="298">
@@ -50701,7 +50990,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>0.7249</v>
+        <v>0.7205</v>
       </c>
     </row>
     <row r="299">
@@ -50726,13 +51015,13 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>0.7121</v>
+        <v>0.7094</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Poole</t>
+          <t>Herne Bay and Sandwich</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -50742,22 +51031,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>0.6797</v>
+        <v>0.6781</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Herne Bay and Sandwich</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -50767,16 +51056,16 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
           <t>con</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>reform</t>
-        </is>
-      </c>
       <c r="E301" t="n">
-        <v>0.6782</v>
+        <v>0.6726</v>
       </c>
     </row>
     <row r="302">
@@ -50801,7 +51090,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>0.6705</v>
+        <v>0.6691</v>
       </c>
     </row>
     <row r="303">
@@ -50826,7 +51115,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>0.6669</v>
+        <v>0.6674</v>
       </c>
     </row>
     <row r="304">
@@ -50851,7 +51140,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>0.6614</v>
+        <v>0.6624</v>
       </c>
     </row>
     <row r="305">
@@ -50876,7 +51165,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>0.6609</v>
+        <v>0.6598000000000001</v>
       </c>
     </row>
     <row r="306">
@@ -50901,7 +51190,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>0.6332</v>
+        <v>0.6304999999999999</v>
       </c>
     </row>
     <row r="307">
@@ -50926,7 +51215,7 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>0.6248</v>
+        <v>0.6221</v>
       </c>
     </row>
     <row r="308">
@@ -50951,7 +51240,7 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>0.6115</v>
+        <v>0.6102</v>
       </c>
     </row>
     <row r="309">
@@ -50976,7 +51265,7 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>0.5844</v>
+        <v>0.5839</v>
       </c>
     </row>
     <row r="310">
@@ -51001,7 +51290,7 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>0.5794</v>
+        <v>0.5744</v>
       </c>
     </row>
     <row r="311">
@@ -51026,7 +51315,7 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>0.553</v>
+        <v>0.5538</v>
       </c>
     </row>
     <row r="312">
@@ -51051,7 +51340,7 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>0.5456</v>
+        <v>0.5458</v>
       </c>
     </row>
     <row r="313">
@@ -51076,7 +51365,7 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>0.534</v>
+        <v>0.5384</v>
       </c>
     </row>
     <row r="314">
@@ -51101,7 +51390,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>0.5316</v>
+        <v>0.5261</v>
       </c>
     </row>
     <row r="315">
@@ -51126,7 +51415,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5064</v>
       </c>
     </row>
   </sheetData>
